--- a/ExcelTable/GameString.xlsx
+++ b/ExcelTable/GameString.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="R4f39b47c31ba48a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rf09e35b159c34e5d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,7 +657,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>x{0} {1}</x:v>
+        <x:v>x {0} = {1}</x:v>
       </x:c>
     </x:row>
     <x:row r="44">

--- a/ExcelTable/GameString.xlsx
+++ b/ExcelTable/GameString.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rf09e35b159c34e5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rab782a655fa04ea4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,7 +657,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>x {0} = {1}</x:v>
+        <x:v>x {0}</x:v>
       </x:c>
     </x:row>
     <x:row r="44">

--- a/ExcelTable/GameString.xlsx
+++ b/ExcelTable/GameString.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rab782a655fa04ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rf8b46dd9b83b4e7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -668,6 +668,14 @@
         <x:v> = {0}</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>777 보너스 {0}회 / +{1}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ExcelTable/GameString.xlsx
+++ b/ExcelTable/GameString.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rf8b46dd9b83b4e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rd5c98c629a4940f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -609,7 +609,7 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
-        <x:v>프리미엄 {0}</x:v>
+        <x:v>{0}</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -617,7 +617,7 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
-        <x:v>일반 {0}</x:v>
+        <x:v>{0}</x:v>
       </x:c>
     </x:row>
     <x:row r="39">

--- a/ExcelTable/GameString.xlsx
+++ b/ExcelTable/GameString.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="Rd5c98c629a4940f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameString" sheetId="1" r:id="R3c4a17bb9eed443e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +45,13 @@
       <x:color rgb="FF92400E"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,8 +78,13 @@
         <x:fgColor rgb="FFFEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -90,11 +100,25 @@
         <x:color rgb="FFD1D5DB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -110,6 +134,9 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -676,6 +703,62 @@
         <x:v>777 보너스 {0}회 / +{1}</x:v>
       </x:c>
     </x:row>
+    <x:row r="46" ht="16.5" customHeight="1">
+      <x:c r="A46" s="17" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B46" s="17" t="str">
+        <x:v>플레이어 기본 공격</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="16.5" customHeight="1">
+      <x:c r="A47" s="17" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B47" s="17" t="str">
+        <x:v>슬라임 접촉 피해</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="16.5" customHeight="1">
+      <x:c r="A48" s="17" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B48" s="17" t="str">
+        <x:v>슬라임 능동 공격</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="16.5" customHeight="1">
+      <x:c r="A49" s="17" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B49" s="17" t="str">
+        <x:v>나</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="16.5" customHeight="1">
+      <x:c r="A50" s="17" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B50" s="17" t="str">
+        <x:v>대상</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="16.5" customHeight="1">
+      <x:c r="A51" s="17" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B51" s="17" t="str">
+        <x:v>원</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="16.5" customHeight="1">
+      <x:c r="A52" s="17" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B52" s="17" t="str">
+        <x:v>사각형</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
